--- a/meta/en/9-5-1.xlsx
+++ b/meta/en/9-5-1.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист 1" sheetId="2" r:id="rId1"/>
+    <sheet name="Лист" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
@@ -16,123 +16,130 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
-    <t>1. Indicator information</t>
-  </si>
-  <si>
-    <t>Goal</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>Indicator</t>
-  </si>
-  <si>
-    <t>2. Data reporter</t>
-  </si>
-  <si>
-    <t>Organization</t>
-  </si>
-  <si>
-    <t>Contact person(s)/Focal point</t>
-  </si>
-  <si>
-    <t>Contact person's email</t>
-  </si>
-  <si>
-    <t>Contact person's phone</t>
-  </si>
-  <si>
-    <t>Organization website (if available)</t>
-  </si>
-  <si>
-    <t>3. Definitions and concepts</t>
-  </si>
-  <si>
-    <t>Definitions</t>
-  </si>
-  <si>
-    <t>Concepts</t>
-  </si>
-  <si>
-    <t>Rationale and interpretation</t>
-  </si>
-  <si>
-    <t>4. Data sources and collection methods</t>
-  </si>
-  <si>
-    <t>Data sources</t>
-  </si>
-  <si>
-    <t>Data collection methods</t>
-  </si>
-  <si>
-    <t>5. Method of computation and other methodological considerations</t>
-  </si>
-  <si>
-    <t>Method of computation</t>
-  </si>
-  <si>
-    <t>Comments and limitations</t>
-  </si>
-  <si>
-    <t>Quality assurance</t>
-  </si>
-  <si>
-    <t>6. Data availability and disaggregation</t>
-  </si>
-  <si>
-    <t>Data availability and gaps</t>
-  </si>
-  <si>
-    <t>Disaggregation</t>
-  </si>
-  <si>
-    <t>7. Comparability with international data/standards</t>
-  </si>
-  <si>
-    <t>8. References and documentation</t>
-  </si>
-  <si>
-    <t>9: Build resilient infrastructure, promote inclusive and sustainable industrialization and foster innovation</t>
-  </si>
-  <si>
-    <t>9.5 Enhance scientific research, upgrade the technological capabilities of industrial sectors in all countries, in particular developing countries, including, by 2030, encouraging innovation and substantially increasing the number of research and development (R&amp;D) workers per 1 million people and public and private research and development (R&amp;D) spending</t>
-  </si>
-  <si>
-    <t>9.5.1 Research and development expenditure as a proportion of GDP</t>
-  </si>
-  <si>
-    <t>Ministry of Finance of the Kyrgyz Republic</t>
-  </si>
-  <si>
-    <t>Research and development (R&amp;D) expenditure as a proportion of Gross Domestic Product (GDP) is the amount of R&amp;D expenditure divided by the total output of the economy.</t>
-  </si>
-  <si>
-    <t>Research and experimental development (R&amp;D) comprise creative and systematic work undertaken in order to increase the stock of knowledge – including knowledge of humankind, culture and society – and to devise new applications of available knowledge.( Frascati Manual, 2015)
-Expenditures on intramural R&amp;D represent the amount of money spent on R&amp;D that is performed within a reporting unit.</t>
-  </si>
-  <si>
-    <t>The indicator is a direct measure of Research and development (R&amp;D) spending.</t>
-  </si>
-  <si>
-    <t>Research and development (R&amp;D) spending is divided by gross domestic product (GDP), expressed as a percentage</t>
-  </si>
-  <si>
-    <t>Research and development (R&amp;D) data need to be collected through surveys, which are expensive, and do not always cover all sectors of performance.</t>
-  </si>
-  <si>
-    <t>National</t>
-  </si>
-  <si>
-    <t>KR National SDG Reporting Platform:  https://sustainabledevelopment-kyrgyzstan.github.io</t>
+    <t>1. Информация об индикаторе</t>
+  </si>
+  <si>
+    <t>Цель</t>
+  </si>
+  <si>
+    <t>Задача</t>
+  </si>
+  <si>
+    <t>Индикатор</t>
+  </si>
+  <si>
+    <t>2. Информация об организации</t>
+  </si>
+  <si>
+    <t>Организация</t>
+  </si>
+  <si>
+    <t>Контактное лицо (лица) / Координатор</t>
+  </si>
+  <si>
+    <t>Электронная почта контактного лица</t>
+  </si>
+  <si>
+    <t>Телефон контактного лица</t>
+  </si>
+  <si>
+    <t>Сайт организации (если есть)</t>
+  </si>
+  <si>
+    <t>3. Определения и понятия</t>
+  </si>
+  <si>
+    <t>Определение</t>
+  </si>
+  <si>
+    <t>Основные понятия:</t>
+  </si>
+  <si>
+    <t>Обоснование и толкование</t>
+  </si>
+  <si>
+    <t>4. Источники данных и методы сбора</t>
+  </si>
+  <si>
+    <t>Источники данных</t>
+  </si>
+  <si>
+    <t>Методы сбора данных</t>
+  </si>
+  <si>
+    <t>5. Метод расчета и другие методологические основы</t>
+  </si>
+  <si>
+    <t>Метод расчета:</t>
+  </si>
+  <si>
+    <t>Комментарий и ограничения:</t>
+  </si>
+  <si>
+    <t>Гарантия качества:</t>
+  </si>
+  <si>
+    <t>6. Доступность данных и дезагрегация</t>
+  </si>
+  <si>
+    <t>Доступность данных и пробелы:</t>
+  </si>
+  <si>
+    <t>Разбивка:</t>
+  </si>
+  <si>
+    <t>7. Сопоставимость с международными данными / стандартами</t>
+  </si>
+  <si>
+    <t>8. Ссылки и документация</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Цель 9: Создание стойкой инфраструктуры, содействие всеохватной и устойчивой индустриализации и инновациям. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5 Активизировать научные исследования, наращивать технологический потенциал промышленных секторов во всех странах, особенно развивающихся странах, в том числе путем стимулирования к 2030 году инновационной деятельности и значительного увеличения числа работников в сфере научно-исследовательских и опытно-конструкторских работ (НИОКР) в расчете на 1 миллион человек, а также государственных и частных расходов на НИОКР </t>
+  </si>
+  <si>
+    <t>9.5.1 Доля расходов на научно-исследовательские и опытно-конструкторские работы в ВВП</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Министерство финансов КР </t>
+  </si>
+  <si>
+    <t>Расходы на исследования и разработки (НИОКР) в процентах от валового внутреннего продукта (ВВП) составляют объем расходов на НИОКР, деленный на общий объем производства экономики</t>
+  </si>
+  <si>
+    <t>Исследования и экспериментальные разработки (НИОКР) включают творческую и систематическую работу, проводимую с целью увеличения объема знаний, в том числе знаний о человечестве, культуре и обществе, а также для разработки новых приложений доступных знаний. (Из Руководства Фраскати от 2015 года).
+Расходы на внутрифирменные НИОКР представляют собой сумму средств, потраченных на НИОКР, которые выполняются в пределах единицы отчетности.</t>
+  </si>
+  <si>
+    <t>Показатель является прямым измерением расходов на исследования и разработки (НИОКР)</t>
+  </si>
+  <si>
+    <t>Сумма расходов на исследования и разработки (НИОКР) делится на объем валового внутреннего продукта (ВВП), выражается в процентах</t>
+  </si>
+  <si>
+    <t>Данные НИОКР необходимо собирать с помощью обследований, которые являются дорогостоящими и не всегда охватывают все сферы деятельности.</t>
+  </si>
+  <si>
+    <t>На республиканском уровне</t>
+  </si>
+  <si>
+    <t>Национальная платформа отчетности ЦУР КР: https://sustainabledevelopment-kyrgyzstan.github.io</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,21 +153,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -214,16 +206,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -231,10 +223,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -547,7 +535,7 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.85546875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="99.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="71.7109375" style="3" customWidth="1"/>
     <col min="3" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
@@ -561,11 +549,11 @@
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="107.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -591,7 +579,7 @@
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -625,7 +613,7 @@
       </c>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:2" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
@@ -633,15 +621,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="201.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="408.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
@@ -659,13 +647,15 @@
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="6"/>
+      <c r="B16" s="5"/>
     </row>
     <row r="17" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="6"/>
+      <c r="B17" s="6" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -673,27 +663,25 @@
       </c>
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="1:2" ht="408.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>34</v>
-      </c>
+      <c r="B20" s="5"/>
     </row>
     <row r="21" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="6"/>
+      <c r="B21" s="5"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -705,7 +693,7 @@
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="6"/>
+      <c r="B23" s="5"/>
     </row>
     <row r="24" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -719,9 +707,9 @@
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="6"/>
-    </row>
-    <row r="26" spans="1:2" ht="243.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="5"/>
+    </row>
+    <row r="26" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>

--- a/meta/en/9-5-1.xlsx
+++ b/meta/en/9-5-1.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист" sheetId="2" r:id="rId1"/>
+    <sheet name="Лист 1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
@@ -16,130 +16,123 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
-    <t>1. Информация об индикаторе</t>
-  </si>
-  <si>
-    <t>Цель</t>
-  </si>
-  <si>
-    <t>Задача</t>
-  </si>
-  <si>
-    <t>Индикатор</t>
-  </si>
-  <si>
-    <t>2. Информация об организации</t>
-  </si>
-  <si>
-    <t>Организация</t>
-  </si>
-  <si>
-    <t>Контактное лицо (лица) / Координатор</t>
-  </si>
-  <si>
-    <t>Электронная почта контактного лица</t>
-  </si>
-  <si>
-    <t>Телефон контактного лица</t>
-  </si>
-  <si>
-    <t>Сайт организации (если есть)</t>
-  </si>
-  <si>
-    <t>3. Определения и понятия</t>
-  </si>
-  <si>
-    <t>Определение</t>
-  </si>
-  <si>
-    <t>Основные понятия:</t>
-  </si>
-  <si>
-    <t>Обоснование и толкование</t>
-  </si>
-  <si>
-    <t>4. Источники данных и методы сбора</t>
-  </si>
-  <si>
-    <t>Источники данных</t>
-  </si>
-  <si>
-    <t>Методы сбора данных</t>
-  </si>
-  <si>
-    <t>5. Метод расчета и другие методологические основы</t>
-  </si>
-  <si>
-    <t>Метод расчета:</t>
-  </si>
-  <si>
-    <t>Комментарий и ограничения:</t>
-  </si>
-  <si>
-    <t>Гарантия качества:</t>
-  </si>
-  <si>
-    <t>6. Доступность данных и дезагрегация</t>
-  </si>
-  <si>
-    <t>Доступность данных и пробелы:</t>
-  </si>
-  <si>
-    <t>Разбивка:</t>
-  </si>
-  <si>
-    <t>7. Сопоставимость с международными данными / стандартами</t>
-  </si>
-  <si>
-    <t>8. Ссылки и документация</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Цель 9: Создание стойкой инфраструктуры, содействие всеохватной и устойчивой индустриализации и инновациям. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5 Активизировать научные исследования, наращивать технологический потенциал промышленных секторов во всех странах, особенно развивающихся странах, в том числе путем стимулирования к 2030 году инновационной деятельности и значительного увеличения числа работников в сфере научно-исследовательских и опытно-конструкторских работ (НИОКР) в расчете на 1 миллион человек, а также государственных и частных расходов на НИОКР </t>
-  </si>
-  <si>
-    <t>9.5.1 Доля расходов на научно-исследовательские и опытно-конструкторские работы в ВВП</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Министерство финансов КР </t>
-  </si>
-  <si>
-    <t>Расходы на исследования и разработки (НИОКР) в процентах от валового внутреннего продукта (ВВП) составляют объем расходов на НИОКР, деленный на общий объем производства экономики</t>
-  </si>
-  <si>
-    <t>Исследования и экспериментальные разработки (НИОКР) включают творческую и систематическую работу, проводимую с целью увеличения объема знаний, в том числе знаний о человечестве, культуре и обществе, а также для разработки новых приложений доступных знаний. (Из Руководства Фраскати от 2015 года).
-Расходы на внутрифирменные НИОКР представляют собой сумму средств, потраченных на НИОКР, которые выполняются в пределах единицы отчетности.</t>
-  </si>
-  <si>
-    <t>Показатель является прямым измерением расходов на исследования и разработки (НИОКР)</t>
-  </si>
-  <si>
-    <t>Сумма расходов на исследования и разработки (НИОКР) делится на объем валового внутреннего продукта (ВВП), выражается в процентах</t>
-  </si>
-  <si>
-    <t>Данные НИОКР необходимо собирать с помощью обследований, которые являются дорогостоящими и не всегда охватывают все сферы деятельности.</t>
-  </si>
-  <si>
-    <t>На республиканском уровне</t>
-  </si>
-  <si>
-    <t>Национальная платформа отчетности ЦУР КР: https://sustainabledevelopment-kyrgyzstan.github.io</t>
+    <t>1. Indicator information</t>
+  </si>
+  <si>
+    <t>Goal</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Indicator</t>
+  </si>
+  <si>
+    <t>2. Data reporter</t>
+  </si>
+  <si>
+    <t>Organization</t>
+  </si>
+  <si>
+    <t>Contact person(s)/Focal point</t>
+  </si>
+  <si>
+    <t>Contact person's email</t>
+  </si>
+  <si>
+    <t>Contact person's phone</t>
+  </si>
+  <si>
+    <t>Organization website (if available)</t>
+  </si>
+  <si>
+    <t>3. Definitions and concepts</t>
+  </si>
+  <si>
+    <t>Definitions</t>
+  </si>
+  <si>
+    <t>Concepts</t>
+  </si>
+  <si>
+    <t>Rationale and interpretation</t>
+  </si>
+  <si>
+    <t>4. Data sources and collection methods</t>
+  </si>
+  <si>
+    <t>Data sources</t>
+  </si>
+  <si>
+    <t>Data collection methods</t>
+  </si>
+  <si>
+    <t>5. Method of computation and other methodological considerations</t>
+  </si>
+  <si>
+    <t>Method of computation</t>
+  </si>
+  <si>
+    <t>Comments and limitations</t>
+  </si>
+  <si>
+    <t>Quality assurance</t>
+  </si>
+  <si>
+    <t>6. Data availability and disaggregation</t>
+  </si>
+  <si>
+    <t>Data availability and gaps</t>
+  </si>
+  <si>
+    <t>Disaggregation</t>
+  </si>
+  <si>
+    <t>7. Comparability with international data/standards</t>
+  </si>
+  <si>
+    <t>8. References and documentation</t>
+  </si>
+  <si>
+    <t>9: Build resilient infrastructure, promote inclusive and sustainable industrialization and foster innovation</t>
+  </si>
+  <si>
+    <t>9.5 Enhance scientific research, upgrade the technological capabilities of industrial sectors in all countries, in particular developing countries, including, by 2030, encouraging innovation and substantially increasing the number of research and development (R&amp;D) workers per 1 million people and public and private research and development (R&amp;D) spending</t>
+  </si>
+  <si>
+    <t>9.5.1 Research and development expenditure as a proportion of GDP</t>
+  </si>
+  <si>
+    <t>Ministry of Finance of the Kyrgyz Republic</t>
+  </si>
+  <si>
+    <t>Research and development (R&amp;D) expenditure as a proportion of Gross Domestic Product (GDP) is the amount of R&amp;D expenditure divided by the total output of the economy.</t>
+  </si>
+  <si>
+    <t>Research and experimental development (R&amp;D) comprise creative and systematic work undertaken in order to increase the stock of knowledge – including knowledge of humankind, culture and society – and to devise new applications of available knowledge.( Frascati Manual, 2015)
+Expenditures on intramural R&amp;D represent the amount of money spent on R&amp;D that is performed within a reporting unit.</t>
+  </si>
+  <si>
+    <t>The indicator is a direct measure of Research and development (R&amp;D) spending.</t>
+  </si>
+  <si>
+    <t>Research and development (R&amp;D) spending is divided by gross domestic product (GDP), expressed as a percentage</t>
+  </si>
+  <si>
+    <t>Research and development (R&amp;D) data need to be collected through surveys, which are expensive, and do not always cover all sectors of performance.</t>
+  </si>
+  <si>
+    <t>National</t>
+  </si>
+  <si>
+    <t>KR National SDG Reporting Platform:  https://sustainabledevelopment-kyrgyzstan.github.io</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,6 +146,21 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -206,16 +214,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -223,6 +231,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -535,7 +547,7 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.85546875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="71.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="99.140625" style="3" customWidth="1"/>
     <col min="3" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
@@ -549,11 +561,11 @@
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="107.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -579,7 +591,7 @@
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -613,7 +625,7 @@
       </c>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
@@ -621,15 +633,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="201.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="408.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
@@ -647,15 +659,13 @@
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="5"/>
+      <c r="B16" s="6"/>
     </row>
     <row r="17" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>33</v>
-      </c>
+      <c r="B17" s="6"/>
     </row>
     <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -663,25 +673,27 @@
       </c>
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="408.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="5"/>
+      <c r="B20" s="6" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="21" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="5"/>
+      <c r="B21" s="6"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -693,7 +705,7 @@
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="5"/>
+      <c r="B23" s="6"/>
     </row>
     <row r="24" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -707,9 +719,9 @@
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="5"/>
-    </row>
-    <row r="26" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="6"/>
+    </row>
+    <row r="26" spans="1:2" ht="243.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
